--- a/Expenses Form 2026.xlsx
+++ b/Expenses Form 2026.xlsx
@@ -911,7 +911,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
